--- a/matching_audit.xlsx
+++ b/matching_audit.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,25 +461,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>similarity</t>
+          <t>nama_similarity</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>alamat_similarity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>aksi</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>nama_lpse</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>alamat_lpse</t>
         </is>
@@ -511,18 +516,21 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,18 +558,21 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H3" t="n">
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,20 +606,23 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -636,18 +650,21 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H5" t="n">
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -681,20 +698,23 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>95.5223880597015</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -722,18 +742,21 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H7" t="n">
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -767,20 +790,23 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>96.62921348314607</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -798,28 +824,39 @@
           <t>CORONG TIMUR, CV</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CORONG TIMUR, CV</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>JALAN RAJAWALI</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JL HB JASSIN</t>
+        </is>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>APPEND_BEDA_ALAMAT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -847,18 +884,21 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H10" t="n">
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -886,18 +926,21 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H11" t="n">
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -931,20 +974,23 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>96.7741935483871</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H12" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -972,18 +1018,21 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1011,18 +1060,21 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H14" t="n">
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1050,18 +1102,21 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H15" t="n">
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1089,18 +1144,21 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H16" t="n">
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1128,18 +1186,21 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H17" t="n">
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1167,18 +1228,21 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H18" t="n">
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1206,18 +1270,21 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H19" t="n">
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1245,18 +1312,21 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H20" t="n">
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1290,20 +1360,23 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1331,18 +1404,21 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H22" t="n">
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1370,18 +1446,21 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H23" t="n">
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1409,18 +1488,21 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H24" t="n">
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1448,18 +1530,21 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H25" t="n">
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1487,18 +1572,21 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H26" t="n">
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1526,18 +1614,21 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H27" t="n">
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1565,18 +1656,21 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H28" t="n">
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1604,18 +1698,21 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H29" t="n">
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1643,18 +1740,21 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H30" t="n">
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1682,18 +1782,21 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H31" t="n">
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1721,18 +1824,21 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H32" t="n">
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1760,18 +1866,21 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H33" t="n">
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1789,28 +1898,39 @@
           <t>AGUNG RAYA, CV</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AGUNG RAYA, CV</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Jalan Cendrawasih Nomor 57</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>JL TRANS SULAWESI</t>
+        </is>
+      </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H34" t="n">
+        <v>54.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>APPEND_BEDA_ALAMAT</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1844,20 +1964,23 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>97.29729729729729</v>
-      </c>
-      <c r="H35" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H35" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1885,18 +2008,21 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H36" t="n">
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1924,18 +2050,21 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H37" t="n">
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1969,20 +2098,23 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>95.89041095890411</v>
-      </c>
-      <c r="H38" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H38" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2010,18 +2142,21 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H39" t="n">
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2049,18 +2184,21 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H40" t="n">
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2094,20 +2232,23 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>95.5223880597015</v>
-      </c>
-      <c r="H41" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H41" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2135,18 +2276,21 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H42" t="n">
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2180,20 +2324,23 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>96.3855421686747</v>
-      </c>
-      <c r="H43" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H43" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2221,18 +2368,21 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H44" t="n">
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2266,20 +2416,23 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>96.875</v>
-      </c>
-      <c r="H45" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H45" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2307,18 +2460,21 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H46" t="n">
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2346,18 +2502,21 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H47" t="n">
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2385,18 +2544,21 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H48" t="n">
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2424,18 +2586,21 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H49" t="n">
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2463,18 +2628,21 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H50" t="n">
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2502,18 +2670,21 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H51" t="n">
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2541,18 +2712,21 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H52" t="n">
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2580,18 +2754,21 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H53" t="n">
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2619,18 +2796,21 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H54" t="n">
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2664,20 +2844,23 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>94.57364341085271</v>
-      </c>
-      <c r="H55" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H55" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2705,18 +2888,21 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H56" t="n">
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2744,18 +2930,21 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H57" t="n">
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2783,18 +2972,21 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H58" t="n">
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2822,18 +3014,21 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H59" t="n">
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2861,18 +3056,21 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H60" t="n">
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2900,18 +3098,21 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2939,18 +3140,21 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H62" t="n">
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2978,18 +3182,21 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H63" t="n">
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3007,28 +3214,39 @@
           <t>MOTIKACI FAMILY GROUP, CV</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MOTIKACI FAMILY GROUP, CV</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>Dusun Pasar Lama, Desa Moluo, Kecamatan Kwandang, Kabupaten Gorontalo Utara.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DSN PASAR LAMA</t>
+        </is>
+      </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H64" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>ENRICH_SF</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3056,18 +3274,21 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H65" t="n">
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3101,20 +3322,23 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>94.33962264150944</v>
-      </c>
-      <c r="H66" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H66" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3148,20 +3372,23 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>95.38461538461539</v>
-      </c>
-      <c r="H67" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H67" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3189,18 +3416,21 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H68" t="n">
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3228,18 +3458,21 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H69" t="n">
+        <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3267,18 +3500,21 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H70" t="n">
+        <v>0</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3306,18 +3542,21 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H71" t="n">
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3351,20 +3590,23 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>98.94736842105263</v>
-      </c>
-      <c r="H72" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H72" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3382,28 +3624,39 @@
           <t>EKA PUTRA, CV</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EKA PUTRA, CV</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Jalan Gagak, depan RM ASTA 6000, Desa Marisa Selatan, Kecamatan Marisa, Kabupaten Pohuwato</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JL GAGAK, DEPAN RM ASTA 6000</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H73" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
+          <t>ENRICH_SF</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3437,20 +3690,23 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>92.78350515463917</v>
-      </c>
-      <c r="H74" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H74" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3478,18 +3734,21 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H75" t="n">
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3517,18 +3776,21 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H76" t="n">
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3546,28 +3808,39 @@
           <t>GOMINA PERMAI INDAH, CV</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GOMINA PERMAI INDAH, CV</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Jalan Nani Wartabone</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JL ALWIE ABDUL JALIL HABIBIE</t>
+        </is>
+      </c>
       <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H77" t="n">
+        <v>51.6</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
+          <t>APPEND_BEDA_ALAMAT</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3591,18 +3864,21 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H78" t="n">
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3626,18 +3902,21 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H79" t="n">
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3665,18 +3944,21 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H80" t="n">
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3704,18 +3986,21 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H81" t="n">
+        <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3749,20 +4034,23 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>95.23809523809524</v>
-      </c>
-      <c r="H82" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H82" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3790,18 +4078,21 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H83" t="n">
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3829,18 +4120,21 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H84" t="n">
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3874,20 +4168,23 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>96</v>
-      </c>
-      <c r="H85" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H85" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I85" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3915,18 +4212,21 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H86" t="n">
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3954,18 +4254,21 @@
       <c r="G87" t="n">
         <v>0</v>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H87" t="n">
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3983,28 +4286,39 @@
           <t>SURYA SINTESIA, CV</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SURYA SINTESIA, CV</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>JALAN PADANG PERUMAHAN GRAHA 42 BLOK E NO.3</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>JL PADANG E NO 3</t>
+        </is>
+      </c>
       <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H88" t="n">
+        <v>71</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+          <t>ENRICH_SF</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4032,18 +4346,21 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H89" t="n">
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4077,20 +4394,23 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>96.7032967032967</v>
-      </c>
-      <c r="H90" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H90" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4118,18 +4438,21 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H91" t="n">
+        <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4157,18 +4480,21 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H92" t="n">
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4196,18 +4522,21 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H93" t="n">
+        <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4217,36 +4546,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>INDAH RAHAYU, CV</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>ALYA BERKAH, CV</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ALYA BERKAH, CV</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>JALAN JENDERAL SUDIRMAN NOMOR 28</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>Jalan Kancil</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JL KANCIL DEPAN KANTOR LURAH TENILO</t>
+        </is>
+      </c>
       <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H94" t="n">
+        <v>85.7</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+          <t>ENRICH_SF</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4256,36 +4596,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NURUL YAKIN, CV</t>
+          <t>INDAH RAHAYU, CV</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jln. Sultan Amai</t>
+          <t>JALAN JENDERAL SUDIRMAN NOMOR 28</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H95" t="n">
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4295,36 +4638,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WAHYU, CV</t>
+          <t>NURUL YAKIN, CV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jl. Kesehatan, Desa Toto Utara</t>
+          <t>Jln. Sultan Amai</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H96" t="n">
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4334,44 +4680,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUNGAI BONE GORONTALO, CV</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>SUNGAI BONE GORONTALO, CV</t>
-        </is>
-      </c>
+          <t>WAHYU, CV</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>JALAN PALMA</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>PERUM BELLE ORASAWA, JL PALMA</t>
-        </is>
-      </c>
+          <t>Jl. Kesehatan, Desa Toto Utara</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>91.17647058823529</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>ENRICH_SF</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4381,36 +4722,47 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAHAYA BULAN, CV</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>SUNGAI BONE GORONTALO, CV</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SUNGAI BONE GORONTALO, CV</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dusun Lamahu</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>JALAN PALMA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>PERUM BELLE ORASAWA, JL PALMA</t>
+        </is>
+      </c>
       <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H98" t="n">
+        <v>84.2</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
+          <t>ENRICH_SF</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4420,44 +4772,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ALLIESSAN, PT</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>ALLIESSAN, PT</t>
-        </is>
-      </c>
+          <t>CAHAYA BULAN, CV</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>JL. SULTAN HASANUDDIN</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>JL SULTAN HASANUDIN</t>
-        </is>
-      </c>
+          <t>Dusun Lamahu</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>97.05882352941177</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>ENRICH_SF</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4472,39 +4819,42 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RAHLIN AULIA MANDIRI, PT</t>
+          <t>ALLIESSAN, PT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RAHLIN AULIA MANDIRI, PT</t>
+          <t>ALLIESSAN, PT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jalan Beringin</t>
+          <t>JL. SULTAN HASANUDDIN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JL BERINGIN KELURAHAN TOMULOBUTAO SELATAN</t>
+          <t>JL SULTAN HASANUDIN</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>91.66666666666667</v>
-      </c>
-      <c r="H100" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H100" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>ENRICH_SF</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4514,36 +4864,47 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ZIITEK, CV</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>RAHLIN AULIA MANDIRI, PT</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RAHLIN AULIA MANDIRI, PT</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Desa Toto Utara, Kecamatan Tilongkabila, Kabupaten Bone Bolango</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>Jalan Beringin</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JL BERINGIN KELURAHAN TOMULOBUTAO SELATAN</t>
+        </is>
+      </c>
       <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H101" t="n">
+        <v>88</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
+          <t>ENRICH_SF</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4553,36 +4914,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USAHA SEJAHTERA, CV</t>
+          <t>ZIITEK, CV</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jl. Pelabuhan</t>
+          <t>Desa Toto Utara, Kecamatan Tilongkabila, Kabupaten Bone Bolango</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>0</v>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H102" t="n">
+        <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4592,36 +4956,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TRIANA, CV</t>
+          <t>USAHA SEJAHTERA, CV</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Perum Azizah Permai Blok I Nomor 3</t>
+          <t>Jl. Pelabuhan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>0</v>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H103" t="n">
+        <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4636,31 +5003,34 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BINTANG ADZKIA, CV</t>
+          <t>TRIANA, CV</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jalan A. Otoluwa</t>
+          <t>Perum Azizah Permai Blok I Nomor 3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>0</v>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>APPEND_NEW</t>
-        </is>
+      <c r="H104" t="n">
+        <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SIJK</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
+          <t>APPEND_NEW</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>SIJK</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4670,40 +5040,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>ANTARIKSA PERSADA, CV</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BINTANG ADZKIA, CV</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Jalan A. Otoluwa</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>91.30434782608695</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>ENRICH_SF_FROM_LPSE</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>LPSE</t>
+          <t>APPEND_NEW</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>ANTARIKSA PERSADA, CV</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Desa Sipatana Kec. Buntulia Kab. Pohuwato</t>
-        </is>
-      </c>
+          <t>SIJK</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4713,42 +5082,41 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ARVID, CV</t>
+          <t>ANTARIKSA PERSADA, CV</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>JL JAMBURA</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>95.23809523809524</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>ENRICH_SF_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>ARVID, CV</t>
-        </is>
-      </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Jln. Jambura</t>
+          <t>ANTARIKSA PERSADA, CV</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Desa Sipatana Kec. Buntulia Kab. Pohuwato</t>
         </is>
       </c>
     </row>
@@ -4760,34 +5128,45 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ARVID, CV</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>JL JAMBURA</t>
+        </is>
+      </c>
       <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H107" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
+          <t>ENRICH_SF_FROM_LPSE</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>AMIN, CV</t>
-        </is>
-      </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Jalan Naniwartabone No:144 Kel Oluhuta Kec Kabila</t>
+          <t>ARVID, CV</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Jln. Jambura</t>
         </is>
       </c>
     </row>
@@ -4799,34 +5178,41 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AMIN, CV</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>SEXY ROAD INDO, CV</t>
-        </is>
-      </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Perum Asabri Blok E no 3, Ulapato A</t>
+          <t>AMIN, CV</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Jalan Naniwartabone No:144 Kel Oluhuta Kec Kabila</t>
         </is>
       </c>
     </row>
@@ -4838,34 +5224,45 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SEXY ROAD INDO, CV</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>PERUM ASABRI BLOK E NOMOR 3</t>
+        </is>
+      </c>
       <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H109" t="n">
+        <v>94.09999999999999</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
+          <t>ENRICH_SF_FROM_LPSE</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>DWI SAMA, CV</t>
-        </is>
-      </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>DESA TALANGO KECAMATAN KABILA</t>
+          <t>SEXY ROAD INDO, CV</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Perum Asabri Blok E no 3, Ulapato A</t>
         </is>
       </c>
     </row>
@@ -4881,30 +5278,41 @@
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DWI SAMA, CV</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>JALAN TAMAN BUAH DESA TALANGO</t>
+        </is>
+      </c>
       <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H110" t="n">
+        <v>58.5</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>RIZKY ADITYA PRATAMA, CV</t>
-        </is>
-      </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Desa Tanah Putih Kecamatan Botupingge</t>
+          <t>DWI SAMA, CV</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>DESA TALANGO KECAMATAN KABILA</t>
         </is>
       </c>
     </row>
@@ -4916,42 +5324,45 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>TULUS MULIA, CV</t>
+          <t>RIZKY ADITYA PRATAMA, CV</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JL GUNUNG BOLIOHUTO</t>
+          <t>JL MUHCLIS RAHIM</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>95.5223880597015</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>ENRICH_SF_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H111" t="n">
+        <v>37.5</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>TULUS MULIA, CV</t>
-        </is>
-      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Jl. Gunung Boliohuto No 96 Rt. 003 Rw. 005 Kel. Biawu Kec. Kota Selatan</t>
+          <t>RIZKY ADITYA PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Desa Tanah Putih Kecamatan Botupingge</t>
         </is>
       </c>
     </row>
@@ -4963,34 +5374,45 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>TULUS MULIA, CV</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JL GUNUNG BOLIOHUTO NO 96</t>
+        </is>
+      </c>
       <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H112" t="n">
+        <v>96</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
+          <t>ENRICH_SF_FROM_LPSE</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>PRIMADONA, CV</t>
-        </is>
-      </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Desa Limbato Kec. Tilamuta</t>
+          <t>TULUS MULIA, CV</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Jl. Gunung Boliohuto No 96 Rt. 003 Rw. 005 Kel. Biawu Kec. Kota Selatan</t>
         </is>
       </c>
     </row>
@@ -5002,34 +5424,41 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>PRIMADONA, CV</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>HADFIR PERKASA, CV</t>
-        </is>
-      </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>PERUM PADENGO PERMAI 6 BLOK C NOMOR 1 TENGGELA KECAMATAN TILANGO</t>
+          <t>PRIMADONA, CV</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Desa Limbato Kec. Tilamuta</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5470,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -5051,24 +5480,27 @@
       <c r="G114" t="n">
         <v>0</v>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
         <is>
           <t>APPEND_NEW_FROM_LPSE</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>MITRA CAHAYA TANAMON, CV</t>
-        </is>
-      </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Jl. Membramo II Kel. Molosifat U Kec. Sipatana</t>
+          <t>HADFIR PERKASA, CV</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>PERUM PADENGO PERMAI 6 BLOK C NOMOR 1 TENGGELA KECAMATAN TILANGO</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5512,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -5090,24 +5522,27 @@
       <c r="G115" t="n">
         <v>0</v>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
         <is>
           <t>APPEND_NEW_FROM_LPSE</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>ANUGERAH BERSAMA, CV</t>
-        </is>
-      </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Jln Basoe Bobihoe</t>
+          <t>MITRA CAHAYA TANAMON, CV</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Jl. Membramo II Kel. Molosifat U Kec. Sipatana</t>
         </is>
       </c>
     </row>
@@ -5129,24 +5564,27 @@
       <c r="G116" t="n">
         <v>0</v>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="inlineStr">
         <is>
           <t>APPEND_NEW_FROM_LPSE</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>FELQIMUN ADIJAYA, CV</t>
-        </is>
-      </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Jln. Brgijen Piola Isa Wongkaditi Timur Kota Utara</t>
+          <t>ANUGERAH BERSAMA, CV</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Jln Basoe Bobihoe</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5596,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -5168,24 +5606,27 @@
       <c r="G117" t="n">
         <v>0</v>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
         <is>
           <t>APPEND_NEW_FROM_LPSE</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>ALL AHAD, CV</t>
-        </is>
-      </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Desa Limbato Kec. Tilamuta Kab. Boalemo</t>
+          <t>FELQIMUN ADIJAYA, CV</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Jln. Brgijen Piola Isa Wongkaditi Timur Kota Utara</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5638,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -5207,24 +5648,27 @@
       <c r="G118" t="n">
         <v>0</v>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>APPEND_NEW_FROM_LPSE</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>SATYA HARDANA, CV</t>
-        </is>
-      </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>PERUM AWARA LILUWO KEC. KOTA TENGAH</t>
+          <t>ALL AHAD, CV</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Desa Limbato Kec. Tilamuta Kab. Boalemo</t>
         </is>
       </c>
     </row>
@@ -5242,36 +5686,39 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RARA BERKAH, CV</t>
+          <t>SATYA HARDANA, CV</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JL KANCIL</t>
+          <t>PERUM AWARA KARYA</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>93.61702127659575</v>
-      </c>
-      <c r="H119" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="H119" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="I119" t="inlineStr">
         <is>
           <t>ENRICH_SF_FROM_LPSE</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>RARA BERKAH, CV</t>
-        </is>
-      </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Jl. Kancil RT.001, RW. 001 Kel. Tenilo Kec. Kota Barat</t>
+          <t>SATYA HARDANA, CV</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>PERUM AWARA LILUWO KEC. KOTA TENGAH</t>
         </is>
       </c>
     </row>
@@ -5287,30 +5734,41 @@
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RARA BERKAH, CV</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JL KANCIL</t>
+        </is>
+      </c>
       <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H120" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
+          <t>ENRICH_SF_FROM_LPSE</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>AZRAM MAJU BERSAMA, CV</t>
-        </is>
-      </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Jln Palama Kel. Libuo Kec. Dungingi</t>
+          <t>RARA BERKAH, CV</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Jl. Kancil RT.001, RW. 001 Kel. Tenilo Kec. Kota Barat</t>
         </is>
       </c>
     </row>
@@ -5326,30 +5784,41 @@
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AZRAM MAJU BERSAMA, CV</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JL PALMA NOMOR 16</t>
+        </is>
+      </c>
       <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="H121" t="n">
+        <v>64.3</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>BINTANG PALMA, CV</t>
-        </is>
-      </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Jln Palma Kel. Libuo Kec. Dungingi Kota Gorontalo</t>
+          <t>AZRAM MAJU BERSAMA, CV</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Jln Palama Kel. Libuo Kec. Dungingi</t>
         </is>
       </c>
     </row>
@@ -5361,32 +5830,93 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BINTANG PALMA, CV</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JL PALMA NO 154</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>100</v>
+      </c>
+      <c r="H122" t="n">
+        <v>72</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ENRICH_SF_FROM_LPSE</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>LPSE</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>BINTANG PALMA, CV</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Jln Palma Kel. Libuo Kec. Dungingi Kota Gorontalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>APPEND_NEW_FROM_LPSE</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ARITO PRATAMA, CV</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>DSN DUHI</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>100</v>
+      </c>
+      <c r="H123" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>APPEND_BEDA_ALAMAT_LPSE</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>LPSE</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>ARITO PRATAMA, CV</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>JL. TRANS SULAWESI DESA MOLOMBULAHE KECAMATAN PAGUYAMAN</t>
         </is>
